--- a/handoff/smoke-test/KHIND_Agent_Smoke_Test_Prompts_v2.xlsx
+++ b/handoff/smoke-test/KHIND_Agent_Smoke_Test_Prompts_v2.xlsx
@@ -844,18 +844,18 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>RAG answer in 1-2 BM sentences, then the location question again. Every RM figure must come from a chunk whose source is the 592L document (khind_rsf600a_chillmaster_592l_knowledge_base.md). That chunk may hold no price: then the agent must say it will check or an officer will confirm, NOT quote other models' prices (RM75/RM95 are ChillMaster Lite 480L prices). USP not repeated.</t>
+          <t>RAG answer in 1-2 BM sentences, then the location question again. The search covers only the 592L document (khind_rsf600a_chillmaster_592l_knowledge_base.md), which gives RTO prices Super Saver RM99/month and Smart Value RM119/month over 60 months (RM4,500 outright). Quote these. The missing-fact line here is a Minor Fail, because the answer is in the document. NEVER RM75/RM95: those are ChillMaster Lite 480L prices (Critical). USP not repeated. No handoff.</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>query_product_info(query mentions ChillMaster 592L) -&gt; status ok</t>
+          <t>query_product_info(query mentions ChillMaster 592L) -&gt; status ok, scope 'product', products ['chillmaster_592l']</t>
         </is>
       </c>
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>No figure from another product's document (check 'source' in the Function Response). Location question repeated. Stage still location.</t>
+          <t>Every chunk 'source' in the Function Response is the 592L document; no figure from another product. Location question repeated. Stage still location; not escalated.</t>
         </is>
       </c>
       <c r="I6" s="4" t="n"/>
@@ -941,13 +941,13 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>advance_purchase_stage() -&gt; status ok, previous_stage 'location', new_stage 'qualification'. query_product_info must NOT be called.</t>
+          <t>advance_purchase_stage(postcode='43000', town='Kajang', state='Selangor') -&gt; status ok, previous_stage 'location', new_stage 'qualification', area. query_product_info must NOT be called.</t>
         </is>
       </c>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Covered verdict; stage = qualification; no RAG call; kerja question asked (no 'slip gaji').</t>
+          <t>Covered verdict; stage = qualification; State customer_location set; no RAG call; kerja question asked (no 'slip gaji').</t>
         </is>
       </c>
       <c r="I8" s="4" t="n"/>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Confirms the details are complete and gives the next step (IC photo, or an officer will follow up). No personal data echoed.</t>
+          <t>The fixed form-complete line, word for word: "Terima kasih, butiran permohonan cik/tuan sudah lengkap! 👍 Boleh hantar *gambar IC depan &amp; belakang* sekarang?". No personal data echoed.</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1177,7 +1177,7 @@
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>State: application_complete=true. Reply asks for the IC photo or confirms submission. PDPA: no echo.</t>
+          <t>State: application_complete=true. Reply = the form-complete line (ends with the IC-photo question). PDPA: no echo.</t>
         </is>
       </c>
       <c r="I13" s="4" t="n"/>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Does NOT resend the full blank form. Confirms the details were received and asks only for anything outstanding (e.g. gambar IC depan belakang).</t>
+          <t>Does NOT resend the full blank form. Confirms the details were received and ends with the IC-photo question ("Boleh hantar *gambar IC depan &amp; belakang* sekarang?" or same meaning).</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       <c r="G14" s="4" t="n"/>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>No second full form in the chat.</t>
+          <t>No second full form in the chat; ends with a question.</t>
         </is>
       </c>
       <c r="I14" s="4" t="n"/>
@@ -1309,13 +1309,13 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>escalate_to_live_agent(label='coverage-unsupported-alternative') -&gt; escalated true, chatwoot 'skipped'; called BEFORE the reply text. query_product_info must NOT be called.</t>
+          <t>advance_purchase_stage(postcode='96800', town='Kapit', state='Sarawak') -&gt; status not_covered; then escalate_to_live_agent(label='coverage-unsupported-alternative') -&gt; escalated true, chatwoot 'skipped'; called BEFORE the reply text. query_product_info must NOT be called.</t>
         </is>
       </c>
       <c r="G16" s="4" t="n"/>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Exact label; State escalated=true and escalation_label=coverage-unsupported-alternative; no 'rakan kongsi'; stage still location.</t>
+          <t>Exact label; State escalated=true, escalation_label=coverage-unsupported-alternative and customer_location set; no 'rakan kongsi'; stage still location.</t>
         </is>
       </c>
       <c r="I16" s="4" t="n"/>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>advance_purchase_stage() -&gt; location to qualification. query_product_info must NOT be called.</t>
+          <t>advance_purchase_stage(postcode='93350', town='Kuching', state='Sarawak') -&gt; status ok, location to qualification. query_product_info must NOT be called.</t>
         </is>
       </c>
       <c r="G17" s="4" t="n"/>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>advance_purchase_stage() -&gt; qualification. query_product_info must NOT be called.</t>
+          <t>advance_purchase_stage(postcode='88000', town='Kota Kinabalu', state='Sabah') -&gt; status ok -&gt; qualification. query_product_info must NOT be called.</t>
         </is>
       </c>
       <c r="G18" s="4" t="n"/>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>escalate_to_live_agent(label='coverage-unsupported-alternative'). query_product_info must NOT be called.</t>
+          <t>advance_purchase_stage(town='Nabawan', state='Sabah') -&gt; status not_covered; then escalate_to_live_agent(label='coverage-unsupported-alternative'). query_product_info must NOT be called.</t>
         </is>
       </c>
       <c r="G19" s="4" t="n"/>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>escalate_to_live_agent(label='coverage-unsupported-alternative'). query_product_info must NOT be called.</t>
+          <t>advance_purchase_stage(postcode='87000', town or state='Labuan') -&gt; status not_covered; then escalate_to_live_agent(label='coverage-unsupported-alternative'). query_product_info must NOT be called.</t>
         </is>
       </c>
       <c r="G20" s="4" t="n"/>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>escalate_to_live_agent(label='coverage-unsupported-alternative'). query_product_info must NOT be called.</t>
+          <t>advance_purchase_stage(state or town='Singapore') -&gt; status not_covered; then escalate_to_live_agent(label='coverage-unsupported-alternative'). query_product_info must NOT be called.</t>
         </is>
       </c>
       <c r="G21" s="4" t="n"/>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>advance_purchase_stage() -&gt; qualification. query_product_info must NOT be called.</t>
+          <t>advance_purchase_stage(postcode='10450', town='Georgetown', state='Pulau Pinang') -&gt; status ok -&gt; qualification. query_product_info must NOT be called.</t>
         </is>
       </c>
       <c r="G22" s="4" t="n"/>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>advance_purchase_stage(state='Sabah') -&gt; status need_town (asks the question in 'ask'), or no tool call</t>
         </is>
       </c>
       <c r="G23" s="4" t="n"/>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>advance_purchase_stage(postcode='96800') -&gt; status need_town (no town worked out from the postcode)</t>
         </is>
       </c>
       <c r="G24" s="4" t="n"/>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>set_product_interest('aircond_kool_series') -&gt; ok, first_time true; then advance_purchase_stage() -&gt; qualification. query_product_info must NOT be called.</t>
+          <t>set_product_interest('aircond_kool_series') -&gt; ok, first_time true; then advance_purchase_stage(town='Kajang', state='Selangor') -&gt; status ok -&gt; qualification. query_product_info must NOT be called.</t>
         </is>
       </c>
       <c r="G25" s="4" t="n"/>
@@ -1764,18 +1764,18 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Product and an uncovered area in one message: one not-covered handoff line (Kapit). The 592L USP may appear above it or be absent; both are acceptable here.</t>
+          <t>Product and an uncovered area in one message: one not-covered handoff line (Kapit), and no USP (code drops the USP on a handoff turn).</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>set_product_interest('chillmaster_592l'), then escalate_to_live_agent(label='coverage-unsupported-alternative'). query_product_info must NOT be called.</t>
+          <t>set_product_interest('chillmaster_592l'), then advance_purchase_stage(town='Kapit', state='Sarawak') -&gt; status not_covered, then escalate_to_live_agent(label='coverage-unsupported-alternative'). query_product_info must NOT be called.</t>
         </is>
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Exact label; escalated=true; one handoff line; no sales question after it.</t>
+          <t>Exact label; escalated=true; one handoff line; no USP; no sales question after it.</t>
         </is>
       </c>
       <c r="I26" s="4" t="n"/>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Shows the full 8-product list in 3 groups inside the reply (not 'see the list above'). No USP dump. May end with the location question or a which-product question.</t>
+          <t>Copies the 8-product list in 3 groups exactly as in Reference &gt; Product list, inside the reply (not 'see the list above'). No USP dump. Ends with the location question, because that step is still pending.</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -2327,7 +2327,7 @@
       <c r="G38" s="4" t="n"/>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>All 8 products listed in the reply; stage unchanged.</t>
+          <t>List identical to the Reference; ends with the location question; stage unchanged.</t>
         </is>
       </c>
       <c r="I38" s="4" t="n"/>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Explains that this scheme covers the 8 listed appliances; no TV or microwave specs or prices invented. If it refers to the list, it shows it.</t>
+          <t>Explains that this rental scheme covers the 8 listed appliances. Does NOT claim that KHIND sells no TV or microwave at all. No TV or microwave specs or prices invented. If it refers to the list, it shows it. Then the location question again.</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -2419,7 +2419,7 @@
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>No hallucinated product; no reference to a list that is not shown.</t>
+          <t>No hallucinated product; no brand-wide claim; no reference to a list that is not shown; location question repeated.</t>
         </is>
       </c>
       <c r="I40" s="4" t="n"/>
@@ -2500,18 +2500,18 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Replies 100% in BM. Likely picks the aircond (USP verbatim once) and answers the price only with figures from the aircond document (khind_acson_knowledge_base.md), then the location question.</t>
+          <t>Replies 100% in BM. Picks the aircond (USP verbatim once). The aircond document (khind_acson_knowledge_base.md) holds no monthly price (only installation charges), so the missing-fact line ("Maaf, maklumat [topik] belum ada dalam sistem saya. Pegawai kami akan sahkan dengan cik/tuan nanti ya 🙏", topic filled in), then the location question. No handoff.</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>set_product_interest('aircond_kool_series') and/or query_product_info</t>
+          <t>set_product_interest('aircond_kool_series'); query_product_info -&gt; scope 'product', products ['aircond_kool_series']. escalate_to_live_agent must NOT be called.</t>
         </is>
       </c>
       <c r="G42" s="4" t="n"/>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>BM only; every RM figure traceable to the aircond document.</t>
+          <t>BM only; no RM figure from another product; not escalated; location question asked.</t>
         </is>
       </c>
       <c r="I42" s="4" t="n"/>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Review 5 ordinary replies from the runs above (not USP, BORANG or handoff lines)</t>
+          <t>Review 5 ordinary replies from the runs above (not USP, BORANG or handoff lines); include A11 and F6</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Does not repeat the stored personal values; says the details are recorded safely and moves on.</t>
+          <t>Does not repeat the stored personal values; says the details are recorded safely and moves on with the IC-photo question.</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2925,7 +2925,7 @@
       <c r="G51" s="4" t="n"/>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>PDPA: no IC or name echoed.</t>
+          <t>PDPA: no IC or name echoed; ends with a question.</t>
         </is>
       </c>
       <c r="I51" s="4" t="n"/>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>ASSUMPTION awaiting the user's confirmation: a pensioner counts as not working, so the not-working handoff line.</t>
+          <t>A pensioner counts as not working (confirmed 2026-09-24), so the not-working handoff line, once.</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -3063,7 +3063,7 @@
       <c r="G54" s="4" t="n"/>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Exact label. If the user decides pensioners count as working, flip this expectation.</t>
+          <t>Exact label; no RM1 promo; no form.</t>
         </is>
       </c>
       <c r="I54" s="4" t="n"/>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>ASSUMPTION awaiting the user's confirmation: self-employed counts as working, so the RM1 line: "Terbaik! 👍 *Pendaftaran hanya RM1*, tiada bayaran lain sekarang. Jom semak kelayakan dulu?". No escalation.</t>
+          <t>Self-employed counts as working (confirmed 2026-09-24), so the RM1 line: "Terbaik! 👍 *Pendaftaran hanya RM1*, tiada bayaran lain sekarang. Jom semak kelayakan dulu?". No escalation.</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -3420,18 +3420,18 @@
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>Switches back without repeating the 592L USP. A weight only if a 592L-document chunk states it; if not, it must not quote ChillMaster Lite figures (80kg / 87kg). Then the kerja question again.</t>
+          <t>Switches back without repeating the 592L USP. The 592L document states Net Weight 85kg (Gross 95kg): quote that. The missing-fact line here is a Minor Fail, because the answer is in the document. Never ChillMaster Lite figures (80kg / 87kg). No handoff. Then the kerja question again.</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>set_product_interest('chillmaster_592l') -&gt; first_time false; query_product_info (592L)</t>
+          <t>set_product_interest('chillmaster_592l') -&gt; first_time false; query_product_info -&gt; scope 'product', products ['chillmaster_592l']. escalate_to_live_agent must NOT be called.</t>
         </is>
       </c>
       <c r="G62" s="4" t="n"/>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>No USP repeat; no figure from another product's document; stage still qualification.</t>
+          <t>State product_interest=chillmaster_592l; no USP repeat; no figure from another product's document; stage still qualification; not escalated.</t>
         </is>
       </c>
       <c r="I62" s="4" t="n"/>
@@ -3523,7 +3523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3778,192 +3778,192 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="27" customHeight="1">
+    <row r="21" ht="40.5" customHeight="1">
       <c r="A21" s="9" t="n"/>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Stage machine errors</t>
+          <t>Coverage statuses</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>advance_purchase_stage returns status 'error' when no product is set or at the end of the stage machine. Designed behaviour.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
+          <t>advance_purchase_stage returns status 'error' when no product is set, and 'need_town' / 'need_state' / 'need_location' when the place is not clear yet (the agent then asks the question in 'ask'). After the location step, a call with no place is a no-op. Designed behaviour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="27" customHeight="1">
       <c r="A22" s="9" t="n"/>
       <c r="B22" s="9" t="inlineStr">
         <is>
+          <t>customer_location in State</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Written by advance_purchase_stage for the Chatwoot handoff note. Expected after any covered or not-covered verdict.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
           <t>Empty State at start</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>A new ADK Web session has no keys; a missing purchase_stage means discovery.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Product number -&gt; canonical key -&gt; RAG source document (for product-identity checks on figures)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>chillmaster_592l</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>KHIND ChillMaster 592L (Side-by-Side)   |   RAG source: khind_rsf600a_chillmaster_592l_knowledge_base.md</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>chillmaster_lite_480l</t>
+          <t>chillmaster_592l</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>ChillMaster Lite 480L (2 Pintu)   |   RAG source: khind_rf480_chillmaster_lite_knowledge_base.md</t>
+          <t>KHIND ChillMaster 592L (Side-by-Side)   |   RAG source: khind_rsf600a_chillmaster_592l_knowledge_base.md</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>chillmaster_x_466l</t>
+          <t>chillmaster_lite_480l</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>ChillMaster X 466L (4 Pintu)   |   RAG source: khind_rfm466a_chillmasterx_466l_knowledge_base.md</t>
+          <t>ChillMaster Lite 480L (2 Pintu)   |   RAG source: khind_rf480_chillmaster_lite_knowledge_base.md</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>washer_dryer_11_7</t>
+          <t>chillmaster_x_466l</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>2-in-1 Washer Dryer 11KG/7KG   |   RAG source: khind_wd1468_washer_dryer_knowledge_base.md</t>
+          <t>ChillMaster X 466L (4 Pintu)   |   RAG source: khind_rfm466a_chillmasterx_466l_knowledge_base.md</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>front_load_9kg</t>
+          <t>washer_dryer_11_7</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Front Load Washer 9KG (basuh sahaja)   |   RAG source: khind_wm1248_9kg_washer_knowledge_base.md</t>
+          <t>2-in-1 Washer Dryer 11KG/7KG   |   RAG source: khind_wd1468_washer_dryer_knowledge_base.md</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>ecowash_top_15kg</t>
+          <t>front_load_9kg</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>EcoWash Top Load 15KG   |   RAG source: khind_wm150a_ecowash15_knowledge_base.md</t>
+          <t>Front Load Washer 9KG (basuh sahaja)   |   RAG source: khind_wm1248_9kg_washer_knowledge_base.md</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>drymaster_9kg</t>
+          <t>ecowash_top_15kg</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>DryMaster Heat Pump Dryer 9KG   |   RAG source: khind_dhp90_drymaster_heatpump_dryer_knowledge_base.md</t>
+          <t>EcoWash Top Load 15KG   |   RAG source: khind_wm150a_ecowash15_knowledge_base.md</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>drymaster_9kg</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>DryMaster Heat Pump Dryer 9KG   |   RAG source: khind_dhp90_drymaster_heatpump_dryer_knowledge_base.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>aircond_kool_series</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>KHIND KOOL Series Inverter Aircond 1.0-2.0HP   |   RAG source: khind_acson_knowledge_base.md</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>Sales stage machine (purchase_stage) - updated 2026-09-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="n"/>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>discovery -&gt; location</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>set_product_interest() on a product pick (the old 'product' stage is legacy and treated as location)</t>
         </is>
       </c>
     </row>
@@ -3971,12 +3971,12 @@
       <c r="A34" s="9" t="n"/>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>location -&gt; qualification</t>
+          <t>discovery -&gt; location</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>advance_purchase_stage() after a COVERED area</t>
+          <t>set_product_interest() on a product pick (the old 'product' stage is legacy and treated as location)</t>
         </is>
       </c>
     </row>
@@ -3984,12 +3984,12 @@
       <c r="A35" s="9" t="n"/>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>qualification -&gt; form</t>
+          <t>location -&gt; qualification</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>optional; the closing fragment covers both stages</t>
+          <t>advance_purchase_stage(postcode, town, state) when code finds the area COVERED</t>
         </is>
       </c>
     </row>
@@ -3997,32 +3997,32 @@
       <c r="A36" s="9" t="n"/>
       <c r="B36" s="9" t="inlineStr">
         <is>
+          <t>qualification -&gt; form</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>optional; the closing fragment covers both stages</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n"/>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
           <t>product switch</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>set_product_interest() at a later stage keeps the stage; the USP and media go out once for the new product</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Approved escalation labels (anything else = tool error)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="n"/>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>coverage-unsupported-alternative</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Area outside the covered lists</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       <c r="A39" s="9" t="n"/>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>not-working</t>
+          <t>coverage-unsupported-alternative</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Customer does not work (new on 2026-09-24; replaces no-payslip-alternative)</t>
+          <t>Area outside the covered lists</t>
         </is>
       </c>
     </row>
@@ -4043,12 +4043,12 @@
       <c r="A40" s="9" t="n"/>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>human-required</t>
+          <t>not-working</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Customer asks for a human</t>
+          <t>Customer does not work (new on 2026-09-24; replaces no-payslip-alternative)</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       <c r="A41" s="9" t="n"/>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>angry-customer</t>
+          <t>human-required</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Complaint or anger</t>
+          <t>Customer asks for a human</t>
         </is>
       </c>
     </row>
@@ -4069,71 +4069,71 @@
       <c r="A42" s="9" t="n"/>
       <c r="B42" s="9" t="inlineStr">
         <is>
+          <t>angry-customer</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Complaint or anger</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="27" customHeight="1">
+      <c r="A43" s="9" t="n"/>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
           <t>rag-error</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>RAG retrieval failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>Coverage rules (prompt-based, NO RAG call)</t>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>RAG retrieval failed (query_product_info status 'error') - ONLY then. A fact that the documents do not hold is NOT a handoff: the agent sends the missing-fact line and carries on.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="n"/>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>Semenanjung 01000-86999</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>ALL areas COVERED</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="27" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Coverage rules (decided in code by advance_purchase_stage, NO RAG call; the model only passes postcode / town / state)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45" s="9" t="n"/>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Sarawak 93xxx-98xxx</t>
+          <t>Semenanjung 01000-86999</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>COVERED only: Sarikei, Asajaya, Miri, Kuching, Kota Samarahan, Balingian Mukah, Sibu, Siburan, Sri Aman, Bau, Serian, Bintulu</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="40.5" customHeight="1">
+          <t>ALL areas COVERED</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="27" customHeight="1">
       <c r="A46" s="9" t="n"/>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Sabah 88xxx-91xxx</t>
+          <t>Sarawak 93xxx-98xxx</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>COVERED only: Kudat, Papar, Menumbok, Ranau, Tuaran, Sandakan, Tambunan, Kota Kinabalu, Bongawan, Keningau, Kuala Penyu, Lahad Datu, Tenom, Penampang, Kota Kinabatangan, Sook, Beaufort, Tawau, Kundasang, Tamparuli, Semporna, Kota Belud, Kunak, Telupid, Beluran, Membakut (Town), Kota Marudu, Sipitang</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
+          <t>COVERED only: Sarikei, Asajaya, Miri, Kuching, Kota Samarahan, Balingian Mukah, Sibu, Siburan, Sri Aman, Bau, Serian, Bintulu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="40.5" customHeight="1">
       <c r="A47" s="9" t="n"/>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>W.P. Labuan 87xxx</t>
+          <t>Sabah 88xxx-91xxx</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>NOT covered</t>
+          <t>COVERED only: Kudat, Papar, Menumbok, Ranau, Tuaran, Sandakan, Tambunan, Kota Kinabalu, Bongawan, Keningau, Kuala Penyu, Lahad Datu, Tenom, Penampang, Kota Kinabatangan, Sook, Beaufort, Tawau, Kundasang, Tamparuli, Semporna, Kota Belud, Kunak, Telupid, Beluran, Membakut (Town), Kota Marudu, Sipitang</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       <c r="A48" s="9" t="n"/>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Outside Malaysia</t>
+          <t>W.P. Labuan 87xxx</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
@@ -4150,49 +4150,49 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="27" customHeight="1">
+    <row r="49">
       <c r="A49" s="9" t="n"/>
       <c r="B49" s="9" t="inlineStr">
         <is>
+          <t>Outside Malaysia</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>NOT covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="27" customHeight="1">
+      <c r="A50" s="9" t="n"/>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
           <t>Unclear area</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>Only a state name, or a Sabah/Sarawak postcode without a town: the agent must ask for the town before deciding</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Only 'Sabah' or 'Sarawak', or a Sabah/Sarawak postcode without a town: the agent must ask for the town before deciding (status need_town). A Peninsular state alone is enough: COVERED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>Fixed customer texts (copied from apps/prompts/khind_prompts.py)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="9" t="n"/>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>Location question</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>Boleh kongsikan Poskod &amp; Kawasan pemasangan untuk saya semak liputan penghantaran percuma? 😊</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="27" customHeight="1">
+    <row r="52">
       <c r="A52" s="9" t="n"/>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Covered line + kerja question</t>
+          <t>Location question</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Baik, kawasan [Kawasan/Poskod] ada dalam liputan penghantaran &amp; pemasangan kami! 🚚✨ Boleh saya tahu cik/tuan bekerja sekarang?</t>
+          <t>Boleh kongsikan Poskod &amp; Kawasan pemasangan untuk saya semak liputan penghantaran percuma? 😊</t>
         </is>
       </c>
     </row>
@@ -4200,38 +4200,38 @@
       <c r="A53" s="9" t="n"/>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Not-covered handoff line</t>
+          <t>Covered line + kerja question</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Maaf sangat cik/tuan, kawasan [Kawasan] belum ada liputan KHIND buat masa ini. 🙏 Pegawai kami akan hubungi cik/tuan nanti ya.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
+          <t>Baik, kawasan [Kawasan/Poskod] ada dalam liputan penghantaran &amp; pemasangan kami! 🚚✨ Boleh saya tahu cik/tuan bekerja sekarang?</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="27" customHeight="1">
       <c r="A54" s="9" t="n"/>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>RM1 line (working)</t>
+          <t>Not-covered handoff line</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Terbaik! 👍 *Pendaftaran hanya RM1*, tiada bayaran lain sekarang. Jom semak kelayakan dulu?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="27" customHeight="1">
+          <t>Maaf sangat cik/tuan, kawasan [Kawasan] belum ada liputan KHIND buat masa ini. 🙏 Pegawai kami akan hubungi cik/tuan nanti ya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
       <c r="A55" s="9" t="n"/>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Not-working handoff line</t>
+          <t>RM1 line (working)</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Faham, cik/tuan. Skim ini memerlukan pemohon yang bekerja. Saya sambungkan cik/tuan kepada pegawai kami untuk bantuan lanjut ya 🙏</t>
+          <t>Terbaik! 👍 *Pendaftaran hanya RM1*, tiada bayaran lain sekarang. Jom semak kelayakan dulu?</t>
         </is>
       </c>
     </row>
@@ -4239,12 +4239,12 @@
       <c r="A56" s="9" t="n"/>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Fallback line: coverage-unsupported-alternative</t>
+          <t>Not-working handoff line</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Maaf sangat cik/tuan, kawasan cik/tuan belum ada liputan KHIND buat masa ini. 🙏 Pegawai kami akan hubungi cik/tuan nanti ya.   (sent by code only when the model writes nothing)</t>
+          <t>Faham, cik/tuan. Skim ini memerlukan pemohon yang bekerja. Saya sambungkan cik/tuan kepada pegawai kami untuk bantuan lanjut ya 🙏</t>
         </is>
       </c>
     </row>
@@ -4252,47 +4252,122 @@
       <c r="A57" s="9" t="n"/>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Fallback line: not-working</t>
+          <t>Missing-fact line (not a handoff)</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Faham, cik/tuan. Skim ini memerlukan pemohon yang bekerja. Saya sambungkan cik/tuan kepada pegawai kami untuk bantuan lanjut ya 🙏   (sent by code only when the model writes nothing)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
+          <t>Maaf, maklumat [topik] belum ada dalam sistem saya. Pegawai kami akan sahkan dengan cik/tuan nanti ya 🙏   ([topik] is filled in; the pending question follows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="27" customHeight="1">
       <c r="A58" s="9" t="n"/>
       <c r="B58" s="9" t="inlineStr">
         <is>
+          <t>Form-complete line</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Terima kasih, butiran permohonan cik/tuan sudah lengkap! 👍 Boleh hantar *gambar IC depan &amp; belakang* sekarang?</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="n"/>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>Town question (need_town)</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Boleh kongsikan nama bandar atau kawasan pemasangan cik/tuan di Sabah/Sarawak? 😊</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="216" customHeight="1">
+      <c r="A60" s="9" t="n"/>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>Product list (copy exactly)</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>❄️ *Peti Sejuk*
+1️⃣ ChillMaster 592L (Side-by-Side)
+2️⃣ ChillMaster Lite 480L (2 Pintu)
+3️⃣ ChillMaster X 466L (4 Pintu)
+🧺 *Mesin Basuh &amp; Pengering*
+4️⃣ 2-in-1 Washer Dryer 11KG/7KG (Cuci &amp; Kering)
+5️⃣ Front Load Washer 9KG (Basuh Sahaja)
+6️⃣ EcoWash Top Load 15KG (Muatan Besar Toto)
+7️⃣ DryMaster Heat Pump Dryer 9KG (Pengering)
+🌬️ *Penyaman Udara*
+8️⃣ KOOL Series Inverter Aircond (1.0HP - 2.0HP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="27" customHeight="1">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>Fallback line: coverage-unsupported-alternative</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>Maaf sangat cik/tuan, kawasan cik/tuan belum ada liputan KHIND buat masa ini. 🙏 Pegawai kami akan hubungi cik/tuan nanti ya.   (sent by code only when the model writes nothing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="27" customHeight="1">
+      <c r="A62" s="9" t="n"/>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Fallback line: not-working</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Faham, cik/tuan. Skim ini memerlukan pemohon yang bekerja. Saya sambungkan cik/tuan kepada pegawai kami untuk bantuan lanjut ya 🙏   (sent by code only when the model writes nothing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="n"/>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
           <t>Fallback line: other labels</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>Baik, saya sambungkan cik/tuan kepada pegawai kami ya. 🙏</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>Fixed USP blocks - must appear word for word, once, on a first pick</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="108" customHeight="1">
-      <c r="A60" s="9" t="inlineStr">
+    <row r="65" ht="108" customHeight="1">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>chillmaster_592l  (4 ✅ lines)</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>*KHIND ChillMaster 592L* ✨
 ✅ Kapasiti besar 592L dengan susunan rak boleh laras, sesuai untuk keluarga besar.
@@ -4302,18 +4377,18 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="94.5" customHeight="1">
-      <c r="A61" s="9" t="inlineStr">
+    <row r="66" ht="94.5" customHeight="1">
+      <c r="A66" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="B66" s="9" t="inlineStr">
         <is>
           <t>chillmaster_lite_480l  (4 ✅ lines)</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>*KHIND ChillMaster Lite 480L* ✨
 ✅ Kapasiti besar 480L - ruang simpanan luas untuk seisi keluarga.
@@ -4323,18 +4398,18 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="121.5" customHeight="1">
-      <c r="A62" s="9" t="inlineStr">
+    <row r="67" ht="121.5" customHeight="1">
+      <c r="A67" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
         <is>
           <t>chillmaster_x_466l  (5 ✅ lines)</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>*KHIND ChillMaster X 466L* ✨
 ✅ Kapasiti besar 466L dengan rekaan moden Multi-Door 4 pintu.
@@ -4345,18 +4420,18 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="148.5" customHeight="1">
-      <c r="A63" s="9" t="inlineStr">
+    <row r="68" ht="148.5" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="B68" s="9" t="inlineStr">
         <is>
           <t>washer_dryer_11_7  (7 ✅ lines)</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C68" s="9" t="inlineStr">
         <is>
           <t>*2-in-1 Washer Dryer KHIND 11KG/7KG* ✨
 ✅ Kapasiti besar - 11KG basuh &amp; 7KG kering
@@ -4369,18 +4444,18 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="148.5" customHeight="1">
-      <c r="A64" s="9" t="inlineStr">
+    <row r="69" ht="148.5" customHeight="1">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B64" s="9" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>front_load_9kg  (6 ✅ lines)</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
         <is>
           <t>*KHIND Front Load Washer 9KG* ✨
 ✅ Kapasiti basuhan 9KG
@@ -4393,18 +4468,18 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="135" customHeight="1">
-      <c r="A65" s="9" t="inlineStr">
+    <row r="70" ht="135" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B70" s="9" t="inlineStr">
         <is>
           <t>ecowash_top_15kg  (5 ✅ lines)</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C70" s="9" t="inlineStr">
         <is>
           <t>*KHIND EcoWash Top Load 15KG* ✨
 ✅ Kapasiti besar 15KG - boleh basuh banyak pakaian sekali gus
@@ -4416,18 +4491,18 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="148.5" customHeight="1">
-      <c r="A66" s="9" t="inlineStr">
+    <row r="71" ht="148.5" customHeight="1">
+      <c r="A71" s="9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B66" s="9" t="inlineStr">
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>drymaster_9kg  (6 ✅ lines)</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr">
+      <c r="C71" s="9" t="inlineStr">
         <is>
           <t>*KHIND DryMaster 9KG (Heat Pump Dryer)* ✨
 ✅ Kapasiti pengeringan 9KG
@@ -4440,18 +4515,18 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="108" customHeight="1">
-      <c r="A67" s="9" t="inlineStr">
+    <row r="72" ht="108" customHeight="1">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="B72" s="9" t="inlineStr">
         <is>
           <t>aircond_kool_series  (4 ✅ lines)</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C72" s="9" t="inlineStr">
         <is>
           <t>*KHIND KOOL Series Air Conditioner* ✨
 ✅ Inverter + 5 Bintang Tenaga - sejuk konsisten, kurang bunyi dan lebih jimat elektrik.
@@ -4461,21 +4536,21 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>BORANG template - must appear exactly (only the Produk value changes)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="378" customHeight="1">
-      <c r="A69" s="9" t="n"/>
-      <c r="B69" s="9" t="inlineStr">
+    <row r="74" ht="378" customHeight="1">
+      <c r="A74" s="9" t="n"/>
+      <c r="B74" s="9" t="inlineStr">
         <is>
           <t>BORANG PERMOHONAN KHIND</t>
         </is>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C74" s="9" t="inlineStr">
         <is>
           <t>BORANG PERMOHONAN KHIND
 =========================
@@ -4501,104 +4576,104 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>Known open issues to watch (2026-09-24)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="27" customHeight="1">
-      <c r="A71" s="9" t="n"/>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>Cross-product figures (A3, G6)</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>RAG ranks the ChillMaster Lite 480L document above the 592L one for 592L price and weight questions, and the 592L chunk has no price or weight. Quoting RM75/RM95 or 80kg/87kg for the 592L is a Critical Fail.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="9" t="n"/>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>PDPA name echo (A8)</t>
-        </is>
-      </c>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t>The model thanked customers by name on 2026-09-20 and 2026-09-24.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="9" t="n"/>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>Duplicate blank form (A11)</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>The full blank form was resent after completion on 2026-09-20.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="9" t="n"/>
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t>Duplicate USP on a switch (G5, G7)</t>
-        </is>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>The model sometimes writes its own product description; code strips it. Count the ✅ lines against this sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="9" t="n"/>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>Product + area in one message (B11, B12)</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>Not tested with the real model before this run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="27" customHeight="1">
+    <row r="76" ht="40.5" customHeight="1">
       <c r="A76" s="9" t="n"/>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Assumptions (F9, F10)</t>
+          <t>Cross-product figures (A3, G6)</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Pensioner = not working, self-employed = working. Awaiting the user's confirmation; flag the outcome, do not treat a mismatch as a defect until confirmed.</t>
+          <t>Failed on the first 2026-09-24 run: whole-corpus search returned the ChillMaster Lite 480L document. Searches are now limited to the product's own document (Function Response: scope 'product'). Quoting RM75/RM95 or 80kg/87kg for the 592L is still a Critical Fail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="27" customHeight="1">
+      <c r="A77" s="9" t="n"/>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>DryMaster prices (D2, C8)</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>The DryMaster document holds two conflicting price tables (RM85/month x 48, or RM105 x 48 and RM135 x 36). Either traces to the DryMaster document: not a Fail, but note it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="n"/>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>PDPA name echo (A8)</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>The model thanked customers by name on 2026-09-20 and 2026-09-24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="n"/>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>Duplicate blank form (A11)</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>The full blank form was resent after completion on 2026-09-20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="n"/>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>Duplicate USP on a switch (G5, G7)</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>The model sometimes writes its own product description; code strips it. Count the ✅ lines against this sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n"/>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>Employment rules (F9, F10)</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>Confirmed 2026-09-24: pensioner = not working, self-employed = working.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A75:C75"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A64:C64"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/handoff/smoke-test/KHIND_Agent_Smoke_Test_Prompts_v2.xlsx
+++ b/handoff/smoke-test/KHIND_Agent_Smoke_Test_Prompts_v2.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>The fixed form-complete line, word for word: "Terima kasih, butiran permohonan cik/tuan sudah lengkap! 👍 Boleh hantar *gambar IC depan &amp; belakang* sekarang?". No personal data echoed.</t>
+          <t>The fixed form-complete line, word for word: "Terima kasih, butiran permohonan cik/tuan sudah lengkap! 👍 Boleh hantar *gambar IC depan &amp; belakang* sekarang? 📸". No personal data echoed.</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Does NOT resend the full blank form. Confirms the details were received and ends with the IC-photo question ("Boleh hantar *gambar IC depan &amp; belakang* sekarang?" or same meaning).</t>
+          <t>Does NOT resend the full blank form. Confirms the details were received and ends with the IC-photo question ("Boleh hantar *gambar IC depan &amp; belakang* sekarang? 📸" or same meaning).</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>advance_purchase_stage(postcode='96800', town='Kapit', state='Sarawak') -&gt; status not_covered; then escalate_to_live_agent(label='coverage-unsupported-alternative') -&gt; escalated true, chatwoot 'skipped'; called BEFORE the reply text. query_product_info must NOT be called.</t>
+          <t>advance_purchase_stage(postcode='96800', town='Kapit', state='Sarawak') -&gt; status not_covered, escalated true, label 'coverage-unsupported-alternative' (the tool hands over itself). escalate_to_live_agent is NOT expected; if the model calls it anyway it returns already_escalated true and makes no second handoff (note it in J, not a Fail). query_product_info must NOT be called.</t>
         </is>
       </c>
       <c r="G16" s="4" t="n"/>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>advance_purchase_stage(town='Nabawan', state='Sabah') -&gt; status not_covered; then escalate_to_live_agent(label='coverage-unsupported-alternative'). query_product_info must NOT be called.</t>
+          <t>advance_purchase_stage(town='Nabawan', state='Sabah') -&gt; status not_covered, escalated true, label 'coverage-unsupported-alternative' (the tool hands over itself). escalate_to_live_agent is NOT expected; if the model calls it anyway it returns already_escalated true and makes no second handoff (note it in J, not a Fail). query_product_info must NOT be called.</t>
         </is>
       </c>
       <c r="G19" s="4" t="n"/>
@@ -1493,13 +1493,13 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>advance_purchase_stage(postcode='87000', town or state='Labuan') -&gt; status not_covered; then escalate_to_live_agent(label='coverage-unsupported-alternative'). query_product_info must NOT be called.</t>
+          <t>advance_purchase_stage(postcode='87000', town or state='Labuan') -&gt; status not_covered, escalated true, label 'coverage-unsupported-alternative' (the tool hands over itself). escalate_to_live_agent is NOT expected; if the model calls it anyway it returns already_escalated true and makes no second handoff (note it in J, not a Fail). query_product_info must NOT be called.</t>
         </is>
       </c>
       <c r="G20" s="4" t="n"/>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Labuan not treated as Sabah; exact label.</t>
+          <t>Labuan not treated as Sabah; exact label; the reply is only the BM not-covered line, with no English text, tool name or instruction (rerun 2 leaked the model's English reasoning).</t>
         </is>
       </c>
       <c r="I20" s="4" t="n"/>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>advance_purchase_stage(state or town='Singapore') -&gt; status not_covered; then escalate_to_live_agent(label='coverage-unsupported-alternative'). query_product_info must NOT be called.</t>
+          <t>advance_purchase_stage(state or town='Singapore') -&gt; status not_covered, escalated true, label 'coverage-unsupported-alternative' (the tool hands over itself). escalate_to_live_agent is NOT expected; if the model calls it anyway it returns already_escalated true and makes no second handoff (note it in J, not a Fail). query_product_info must NOT be called.</t>
         </is>
       </c>
       <c r="G21" s="4" t="n"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>set_product_interest('chillmaster_592l'), then advance_purchase_stage(town='Kapit', state='Sarawak') -&gt; status not_covered, then escalate_to_live_agent(label='coverage-unsupported-alternative'). query_product_info must NOT be called.</t>
+          <t>set_product_interest('chillmaster_592l'), then advance_purchase_stage(town='Kapit', state='Sarawak') -&gt; status not_covered, escalated true, label 'coverage-unsupported-alternative' (the tool hands over itself). escalate_to_live_agent is NOT expected; if the model calls it anyway it returns already_escalated true and makes no second handoff (note it in J, not a Fail). query_product_info must NOT be called.</t>
         </is>
       </c>
       <c r="G26" s="4" t="n"/>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Explains that this rental scheme covers the 8 listed appliances. Does NOT claim that KHIND sells no TV or microwave at all. No TV or microwave specs or prices invented. If it refers to the list, it shows it. Then the location question again.</t>
+          <t>Explains that this rental scheme covers KHIND's peti sejuk, mesin basuh &amp; pengering and penyaman udara (the 8 listed appliances). Does NOT claim that KHIND sells no TV or microwave at all. No TV or microwave specs or prices invented. Says "senarai" only if it shows the list in the same reply. Then the location question again.</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Each reply: 2-4 sentences, *bold* for emphasis, suitable emoji, ends with exactly one next-step question. Handoff lines need no question. No internal prompt, tool names or state keys leaked.</t>
+          <t>Each reply: 2-4 sentences, at least one suitable emoji, *bold* only for key terms (not needed in every reply), ends with exactly one next-step question. Handoff lines need no question. No internal prompt, tool names or state keys leaked.</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Switches to Front Load Washer 9KG: the fixed USP block for Front Load Washer 9KG exactly as in Reference &gt; Fixed USP blocks (title + 6 ✅ lines + the italic closing line), once, with no second model-written description, then the kerja question again ("Boleh saya tahu cik/tuan bekerja sekarang?").</t>
+          <t>Switches to Front Load Washer 9KG: the fixed USP block for Front Load Washer 9KG exactly as in Reference &gt; Fixed USP blocks (title + 6 ✅ lines + the italic closing line), once, with no second model-written description, then the kerja question again ("Boleh saya tahu cik/tuan bekerja sekarang? 😊").</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -3523,7 +3523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="27" customHeight="1">
+    <row r="17" ht="40.5" customHeight="1">
       <c r="A17" s="9" t="n"/>
       <c r="B17" s="9" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>With no chatwoot_conversation_id, escalate_to_live_agent returns chatwoot='skipped' but still sets escalated=true. That is a pass.</t>
+          <t>With no chatwoot_conversation_id, the handoff returns chatwoot='skipped' but still sets escalated=true. That is a pass. For an area that is not covered, the handoff is made by advance_purchase_stage itself: its response shows escalated=true and the label.</t>
         </is>
       </c>
     </row>
@@ -3752,16 +3752,16 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="27" customHeight="1">
+    <row r="19" ht="40.5" customHeight="1">
       <c r="A19" s="9" t="n"/>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Two handoff lines in ADK Web</t>
+          <t>Text beside a coverage or handoff call</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>ADK Web shows every event. If the model writes a handoff line with the tool call and another after it, production keeps only the first (build_reply). Note it in J; not a Fail.</t>
+          <t>Code removes any text the model writes in the same event as an advance_purchase_stage or escalate_to_live_agent Function Call, in ADK Web and in production. The handoff line comes after the tool. Visible text in such an event is a Fail (Major).</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="27" customHeight="1">
       <c r="A39" s="9" t="n"/>
       <c r="B39" s="9" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Area outside the covered lists</t>
+          <t>Area outside the covered lists. Applied by advance_purchase_stage itself (status 'not_covered', escalated=true); the model does not call escalate_to_live_agent for it.</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Terima kasih, butiran permohonan cik/tuan sudah lengkap! 👍 Boleh hantar *gambar IC depan &amp; belakang* sekarang?</t>
+          <t>Terima kasih, butiran permohonan cik/tuan sudah lengkap! 👍 Boleh hantar *gambar IC depan &amp; belakang* sekarang? 📸</t>
         </is>
       </c>
     </row>
@@ -4287,14 +4287,53 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="216" customHeight="1">
+    <row r="60">
       <c r="A60" s="9" t="n"/>
       <c r="B60" s="9" t="inlineStr">
         <is>
+          <t>Postcode question (need_state)</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Boleh kongsikan poskod kawasan pemasangan cik/tuan? 😊</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>Kerja question (alone)</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>Boleh saya tahu cik/tuan bekerja sekarang? 😊</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="n"/>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>IC-photo question (after the form)</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Boleh hantar *gambar IC depan &amp; belakang* sekarang? 📸</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="216" customHeight="1">
+      <c r="A63" s="9" t="n"/>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
           <t>Product list (copy exactly)</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>❄️ *Peti Sejuk*
 1️⃣ ChillMaster 592L (Side-by-Side)
@@ -4310,64 +4349,64 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="27" customHeight="1">
-      <c r="A61" s="9" t="n"/>
-      <c r="B61" s="9" t="inlineStr">
+    <row r="64" ht="27" customHeight="1">
+      <c r="A64" s="9" t="n"/>
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>Fallback line: coverage-unsupported-alternative</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>Maaf sangat cik/tuan, kawasan cik/tuan belum ada liputan KHIND buat masa ini. 🙏 Pegawai kami akan hubungi cik/tuan nanti ya.   (sent by code only when the model writes nothing)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="27" customHeight="1">
-      <c r="A62" s="9" t="n"/>
-      <c r="B62" s="9" t="inlineStr">
+    <row r="65" ht="27" customHeight="1">
+      <c r="A65" s="9" t="n"/>
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>Fallback line: not-working</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>Faham, cik/tuan. Skim ini memerlukan pemohon yang bekerja. Saya sambungkan cik/tuan kepada pegawai kami untuk bantuan lanjut ya 🙏   (sent by code only when the model writes nothing)</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="9" t="n"/>
-      <c r="B63" s="9" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="9" t="n"/>
+      <c r="B66" s="9" t="inlineStr">
         <is>
           <t>Fallback line: other labels</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>Baik, saya sambungkan cik/tuan kepada pegawai kami ya. 🙏</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>Fixed USP blocks - must appear word for word, once, on a first pick</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="108" customHeight="1">
-      <c r="A65" s="9" t="inlineStr">
+    <row r="68" ht="108" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B68" s="9" t="inlineStr">
         <is>
           <t>chillmaster_592l  (4 ✅ lines)</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C68" s="9" t="inlineStr">
         <is>
           <t>*KHIND ChillMaster 592L* ✨
 ✅ Kapasiti besar 592L dengan susunan rak boleh laras, sesuai untuk keluarga besar.
@@ -4377,18 +4416,18 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="94.5" customHeight="1">
-      <c r="A66" s="9" t="inlineStr">
+    <row r="69" ht="94.5" customHeight="1">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B66" s="9" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>chillmaster_lite_480l  (4 ✅ lines)</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
         <is>
           <t>*KHIND ChillMaster Lite 480L* ✨
 ✅ Kapasiti besar 480L - ruang simpanan luas untuk seisi keluarga.
@@ -4398,18 +4437,18 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="121.5" customHeight="1">
-      <c r="A67" s="9" t="inlineStr">
+    <row r="70" ht="121.5" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="B70" s="9" t="inlineStr">
         <is>
           <t>chillmaster_x_466l  (5 ✅ lines)</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C70" s="9" t="inlineStr">
         <is>
           <t>*KHIND ChillMaster X 466L* ✨
 ✅ Kapasiti besar 466L dengan rekaan moden Multi-Door 4 pintu.
@@ -4420,18 +4459,18 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="148.5" customHeight="1">
-      <c r="A68" s="9" t="inlineStr">
+    <row r="71" ht="148.5" customHeight="1">
+      <c r="A71" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>washer_dryer_11_7  (7 ✅ lines)</t>
         </is>
       </c>
-      <c r="C68" s="9" t="inlineStr">
+      <c r="C71" s="9" t="inlineStr">
         <is>
           <t>*2-in-1 Washer Dryer KHIND 11KG/7KG* ✨
 ✅ Kapasiti besar - 11KG basuh &amp; 7KG kering
@@ -4444,18 +4483,18 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="148.5" customHeight="1">
-      <c r="A69" s="9" t="inlineStr">
+    <row r="72" ht="148.5" customHeight="1">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B69" s="9" t="inlineStr">
+      <c r="B72" s="9" t="inlineStr">
         <is>
           <t>front_load_9kg  (6 ✅ lines)</t>
         </is>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C72" s="9" t="inlineStr">
         <is>
           <t>*KHIND Front Load Washer 9KG* ✨
 ✅ Kapasiti basuhan 9KG
@@ -4468,18 +4507,18 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="135" customHeight="1">
-      <c r="A70" s="9" t="inlineStr">
+    <row r="73" ht="135" customHeight="1">
+      <c r="A73" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr">
+      <c r="B73" s="9" t="inlineStr">
         <is>
           <t>ecowash_top_15kg  (5 ✅ lines)</t>
         </is>
       </c>
-      <c r="C70" s="9" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
         <is>
           <t>*KHIND EcoWash Top Load 15KG* ✨
 ✅ Kapasiti besar 15KG - boleh basuh banyak pakaian sekali gus
@@ -4491,18 +4530,18 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="148.5" customHeight="1">
-      <c r="A71" s="9" t="inlineStr">
+    <row r="74" ht="148.5" customHeight="1">
+      <c r="A74" s="9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B71" s="9" t="inlineStr">
+      <c r="B74" s="9" t="inlineStr">
         <is>
           <t>drymaster_9kg  (6 ✅ lines)</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C74" s="9" t="inlineStr">
         <is>
           <t>*KHIND DryMaster 9KG (Heat Pump Dryer)* ✨
 ✅ Kapasiti pengeringan 9KG
@@ -4515,18 +4554,18 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="108" customHeight="1">
-      <c r="A72" s="9" t="inlineStr">
+    <row r="75" ht="108" customHeight="1">
+      <c r="A75" s="9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B72" s="9" t="inlineStr">
+      <c r="B75" s="9" t="inlineStr">
         <is>
           <t>aircond_kool_series  (4 ✅ lines)</t>
         </is>
       </c>
-      <c r="C72" s="9" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>*KHIND KOOL Series Air Conditioner* ✨
 ✅ Inverter + 5 Bintang Tenaga - sejuk konsisten, kurang bunyi dan lebih jimat elektrik.
@@ -4536,21 +4575,21 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="8" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>BORANG template - must appear exactly (only the Produk value changes)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="378" customHeight="1">
-      <c r="A74" s="9" t="n"/>
-      <c r="B74" s="9" t="inlineStr">
+    <row r="77" ht="378" customHeight="1">
+      <c r="A77" s="9" t="n"/>
+      <c r="B77" s="9" t="inlineStr">
         <is>
           <t>BORANG PERMOHONAN KHIND</t>
         </is>
       </c>
-      <c r="C74" s="9" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>BORANG PERMOHONAN KHIND
 =========================
@@ -4576,62 +4615,23 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>Known open issues to watch (2026-09-24)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="40.5" customHeight="1">
-      <c r="A76" s="9" t="n"/>
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t>Cross-product figures (A3, G6)</t>
-        </is>
-      </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t>Failed on the first 2026-09-24 run: whole-corpus search returned the ChillMaster Lite 480L document. Searches are now limited to the product's own document (Function Response: scope 'product'). Quoting RM75/RM95 or 80kg/87kg for the 592L is still a Critical Fail.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="27" customHeight="1">
-      <c r="A77" s="9" t="n"/>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t>DryMaster prices (D2, C8)</t>
-        </is>
-      </c>
-      <c r="C77" s="9" t="inlineStr">
-        <is>
-          <t>The DryMaster document holds two conflicting price tables (RM85/month x 48, or RM105 x 48 and RM135 x 36). Either traces to the DryMaster document: not a Fail, but note it.</t>
-        </is>
-      </c>
-    </row>
     <row r="78">
-      <c r="A78" s="9" t="n"/>
-      <c r="B78" s="9" t="inlineStr">
-        <is>
-          <t>PDPA name echo (A8)</t>
-        </is>
-      </c>
-      <c r="C78" s="9" t="inlineStr">
-        <is>
-          <t>The model thanked customers by name on 2026-09-20 and 2026-09-24.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>Known open issues to watch (2026-09-24, after rerun 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="40.5" customHeight="1">
       <c r="A79" s="9" t="n"/>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Duplicate blank form (A11)</t>
+          <t>Coverage handoff (B2, B5-B7, B12)</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>The full blank form was resent after completion on 2026-09-20.</t>
+          <t>Changed after rerun 2: advance_purchase_stage hands over itself. Rerun 2 had B12 with no handoff and a USP on top, and B6 with the model's English reasoning as the reply. Check the Function Response and State, and that the reply is only the not-covered line.</t>
         </is>
       </c>
     </row>
@@ -4639,12 +4639,12 @@
       <c r="A80" s="9" t="n"/>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Duplicate USP on a switch (G5, G7)</t>
+          <t>Out-of-range items (D6)</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>The model sometimes writes its own product description; code strips it. Count the ✅ lines against this sheet.</t>
+          <t>Rerun 2 said "8 produk dalam senarai kami" without the list.</t>
         </is>
       </c>
     </row>
@@ -4652,10 +4652,88 @@
       <c r="A81" s="9" t="n"/>
       <c r="B81" s="9" t="inlineStr">
         <is>
+          <t>Style (E4)</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>Rerun 2: no bold in A4, no emoji in A11 and F6. Now every reply needs an emoji; bold is only for key terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="40.5" customHeight="1">
+      <c r="A82" s="9" t="n"/>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>Cross-product figures (A3, G6)</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>Failed on the first 2026-09-24 run: whole-corpus search returned the ChillMaster Lite 480L document. Searches are now limited to the product's own document (Function Response: scope 'product'). Quoting RM75/RM95 or 80kg/87kg for the 592L is still a Critical Fail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="27" customHeight="1">
+      <c r="A83" s="9" t="n"/>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>DryMaster prices (D2, C8)</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>The DryMaster document holds two conflicting price tables (RM85/month x 48, or RM105 x 48 and RM135 x 36). Either traces to the DryMaster document: not a Fail, but note it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="27" customHeight="1">
+      <c r="A84" s="9" t="n"/>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>PDPA name echo (A8)</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>The model thanked customers by name on 2026-09-20 and 2026-09-24, and in scripted form-step runs after rerun 2. Read the reply word by word.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="n"/>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>Duplicate blank form (A11)</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>The full blank form was resent after completion on 2026-09-20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="n"/>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>Duplicate USP on a switch (G5, G7)</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>The model sometimes writes its own product description; code strips it. Count the ✅ lines against this sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="n"/>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
           <t>Employment rules (F9, F10)</t>
         </is>
       </c>
-      <c r="C81" s="9" t="inlineStr">
+      <c r="C87" s="9" t="inlineStr">
         <is>
           <t>Confirmed 2026-09-24: pensioner = not working, self-employed = working.</t>
         </is>
@@ -4663,17 +4741,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A76:C76"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A75:C75"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A78:C78"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A64:C64"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/handoff/smoke-test/KHIND_Agent_Smoke_Test_Prompts_v2.xlsx
+++ b/handoff/smoke-test/KHIND_Agent_Smoke_Test_Prompts_v2.xlsx
@@ -1861,13 +1861,13 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>set_product_interest('aircond_kool_series')</t>
+          <t>set_product_interest('aircond_kool_series'), or query_product_info alone: with no active product it selects the product its query names (its response shows product_selected 'aircond_kool_series')</t>
         </is>
       </c>
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Selection tool fired with the aircond key; USP verbatim.</t>
+          <t>Aircond selected (set_product_interest, or product_selected in the query_product_info response); USP verbatim.</t>
         </is>
       </c>
       <c r="I28" s="4" t="n"/>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>set_product_interest('aircond_kool_series'); query_product_info -&gt; scope 'product', products ['aircond_kool_series']. escalate_to_live_agent must NOT be called.</t>
+          <t>set_product_interest('aircond_kool_series') (or query_product_info alone: with no active product it selects the product its query names (its response shows product_selected 'aircond_kool_series')); query_product_info -&gt; scope 'product', products ['aircond_kool_series']. escalate_to_live_agent must NOT be called.</t>
         </is>
       </c>
       <c r="G42" s="4" t="n"/>
@@ -3523,7 +3523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3782,201 +3782,201 @@
       <c r="A21" s="9" t="n"/>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Coverage statuses</t>
+          <t>Pick by search</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>advance_purchase_stage returns status 'error' when no product is set, and 'need_town' / 'need_state' / 'need_location' when the place is not clear yet (the agent then asks the question in 'ask'). After the location step, a call with no place is a no-op. Designed behaviour.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="27" customHeight="1">
+          <t>With no active product, a query_product_info call that names one product selects it (product_selected in its response). No separate set_product_interest call is needed; the USP and the location question follow as for any pick.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40.5" customHeight="1">
       <c r="A22" s="9" t="n"/>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>customer_location in State</t>
+          <t>Coverage statuses</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Written by advance_purchase_stage for the Chatwoot handoff note. Expected after any covered or not-covered verdict.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
+          <t>advance_purchase_stage returns status 'error' when no product is set, and 'need_town' / 'need_state' / 'need_location' when the place is not clear yet (the agent then asks the question in 'ask'). After the location step, a call with no place is a no-op. Designed behaviour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1">
       <c r="A23" s="9" t="n"/>
       <c r="B23" s="9" t="inlineStr">
         <is>
+          <t>customer_location in State</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Written by advance_purchase_stage for the Chatwoot handoff note. Expected after any covered or not-covered verdict.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
           <t>Empty State at start</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>A new ADK Web session has no keys; a missing purchase_stage means discovery.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Product number -&gt; canonical key -&gt; RAG source document (for product-identity checks on figures)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>chillmaster_592l</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>KHIND ChillMaster 592L (Side-by-Side)   |   RAG source: khind_rsf600a_chillmaster_592l_knowledge_base.md</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>chillmaster_lite_480l</t>
+          <t>chillmaster_592l</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>ChillMaster Lite 480L (2 Pintu)   |   RAG source: khind_rf480_chillmaster_lite_knowledge_base.md</t>
+          <t>KHIND ChillMaster 592L (Side-by-Side)   |   RAG source: khind_rsf600a_chillmaster_592l_knowledge_base.md</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>chillmaster_x_466l</t>
+          <t>chillmaster_lite_480l</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>ChillMaster X 466L (4 Pintu)   |   RAG source: khind_rfm466a_chillmasterx_466l_knowledge_base.md</t>
+          <t>ChillMaster Lite 480L (2 Pintu)   |   RAG source: khind_rf480_chillmaster_lite_knowledge_base.md</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>washer_dryer_11_7</t>
+          <t>chillmaster_x_466l</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>2-in-1 Washer Dryer 11KG/7KG   |   RAG source: khind_wd1468_washer_dryer_knowledge_base.md</t>
+          <t>ChillMaster X 466L (4 Pintu)   |   RAG source: khind_rfm466a_chillmasterx_466l_knowledge_base.md</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>front_load_9kg</t>
+          <t>washer_dryer_11_7</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Front Load Washer 9KG (basuh sahaja)   |   RAG source: khind_wm1248_9kg_washer_knowledge_base.md</t>
+          <t>2-in-1 Washer Dryer 11KG/7KG   |   RAG source: khind_wd1468_washer_dryer_knowledge_base.md</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>ecowash_top_15kg</t>
+          <t>front_load_9kg</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>EcoWash Top Load 15KG   |   RAG source: khind_wm150a_ecowash15_knowledge_base.md</t>
+          <t>Front Load Washer 9KG (basuh sahaja)   |   RAG source: khind_wm1248_9kg_washer_knowledge_base.md</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>drymaster_9kg</t>
+          <t>ecowash_top_15kg</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>DryMaster Heat Pump Dryer 9KG   |   RAG source: khind_dhp90_drymaster_heatpump_dryer_knowledge_base.md</t>
+          <t>EcoWash Top Load 15KG   |   RAG source: khind_wm150a_ecowash15_knowledge_base.md</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>drymaster_9kg</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>DryMaster Heat Pump Dryer 9KG   |   RAG source: khind_dhp90_drymaster_heatpump_dryer_knowledge_base.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>aircond_kool_series</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>KHIND KOOL Series Inverter Aircond 1.0-2.0HP   |   RAG source: khind_acson_knowledge_base.md</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>Sales stage machine (purchase_stage) - updated 2026-09-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="n"/>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>discovery -&gt; location</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>set_product_interest() on a product pick (the old 'product' stage is legacy and treated as location)</t>
         </is>
       </c>
     </row>
@@ -3984,12 +3984,12 @@
       <c r="A35" s="9" t="n"/>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>location -&gt; qualification</t>
+          <t>discovery -&gt; location</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>advance_purchase_stage(postcode, town, state) when code finds the area COVERED</t>
+          <t>set_product_interest() on a product pick (the old 'product' stage is legacy and treated as location)</t>
         </is>
       </c>
     </row>
@@ -3997,12 +3997,12 @@
       <c r="A36" s="9" t="n"/>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>qualification -&gt; form</t>
+          <t>location -&gt; qualification</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>optional; the closing fragment covers both stages</t>
+          <t>advance_purchase_stage(postcode, town, state) when code finds the area COVERED</t>
         </is>
       </c>
     </row>
@@ -4010,45 +4010,45 @@
       <c r="A37" s="9" t="n"/>
       <c r="B37" s="9" t="inlineStr">
         <is>
+          <t>qualification -&gt; form</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>optional; the closing fragment covers both stages</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n"/>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
           <t>product switch</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>set_product_interest() at a later stage keeps the stage; the USP and media go out once for the new product</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Approved escalation labels (anything else = tool error)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="27" customHeight="1">
-      <c r="A39" s="9" t="n"/>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>coverage-unsupported-alternative</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>Area outside the covered lists. Applied by advance_purchase_stage itself (status 'not_covered', escalated=true); the model does not call escalate_to_live_agent for it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
+    <row r="40" ht="27" customHeight="1">
       <c r="A40" s="9" t="n"/>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>not-working</t>
+          <t>coverage-unsupported-alternative</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Customer does not work (new on 2026-09-24; replaces no-payslip-alternative)</t>
+          <t>Area outside the covered lists. Applied by advance_purchase_stage itself (status 'not_covered', escalated=true); the model does not call escalate_to_live_agent for it.</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       <c r="A41" s="9" t="n"/>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>human-required</t>
+          <t>not-working</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Customer asks for a human</t>
+          <t>Customer does not work (new on 2026-09-24; replaces no-payslip-alternative)</t>
         </is>
       </c>
     </row>
@@ -4069,84 +4069,84 @@
       <c r="A42" s="9" t="n"/>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>angry-customer</t>
+          <t>human-required</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Complaint or anger</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="27" customHeight="1">
+          <t>Customer asks for a human</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43" s="9" t="n"/>
       <c r="B43" s="9" t="inlineStr">
         <is>
+          <t>angry-customer</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Complaint or anger</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="27" customHeight="1">
+      <c r="A44" s="9" t="n"/>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
           <t>rag-error</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>RAG retrieval failed (query_product_info status 'error') - ONLY then. A fact that the documents do not hold is NOT a handoff: the agent sends the missing-fact line and carries on.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>Coverage rules (decided in code by advance_purchase_stage, NO RAG call; the model only passes postcode / town / state)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="9" t="n"/>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>Semenanjung 01000-86999</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>ALL areas COVERED</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="27" customHeight="1">
+    <row r="46">
       <c r="A46" s="9" t="n"/>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Sarawak 93xxx-98xxx</t>
+          <t>Semenanjung 01000-86999</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>COVERED only: Sarikei, Asajaya, Miri, Kuching, Kota Samarahan, Balingian Mukah, Sibu, Siburan, Sri Aman, Bau, Serian, Bintulu</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="40.5" customHeight="1">
+          <t>ALL areas COVERED</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="27" customHeight="1">
       <c r="A47" s="9" t="n"/>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Sabah 88xxx-91xxx</t>
+          <t>Sarawak 93xxx-98xxx</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>COVERED only: Kudat, Papar, Menumbok, Ranau, Tuaran, Sandakan, Tambunan, Kota Kinabalu, Bongawan, Keningau, Kuala Penyu, Lahad Datu, Tenom, Penampang, Kota Kinabatangan, Sook, Beaufort, Tawau, Kundasang, Tamparuli, Semporna, Kota Belud, Kunak, Telupid, Beluran, Membakut (Town), Kota Marudu, Sipitang</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
+          <t>COVERED only: Sarikei, Asajaya, Miri, Kuching, Kota Samarahan, Balingian Mukah, Sibu, Siburan, Sri Aman, Bau, Serian, Bintulu</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40.5" customHeight="1">
       <c r="A48" s="9" t="n"/>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>W.P. Labuan 87xxx</t>
+          <t>Sabah 88xxx-91xxx</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>NOT covered</t>
+          <t>COVERED only: Kudat, Papar, Menumbok, Ranau, Tuaran, Sandakan, Tambunan, Kota Kinabalu, Bongawan, Keningau, Kuala Penyu, Lahad Datu, Tenom, Penampang, Kota Kinabatangan, Sook, Beaufort, Tawau, Kundasang, Tamparuli, Semporna, Kota Belud, Kunak, Telupid, Beluran, Membakut (Town), Kota Marudu, Sipitang</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
       <c r="A49" s="9" t="n"/>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Outside Malaysia</t>
+          <t>W.P. Labuan 87xxx</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
@@ -4163,49 +4163,49 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="27" customHeight="1">
+    <row r="50">
       <c r="A50" s="9" t="n"/>
       <c r="B50" s="9" t="inlineStr">
         <is>
+          <t>Outside Malaysia</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>NOT covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="27" customHeight="1">
+      <c r="A51" s="9" t="n"/>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
           <t>Unclear area</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>Only 'Sabah' or 'Sarawak', or a Sabah/Sarawak postcode without a town: the agent must ask for the town before deciding (status need_town). A Peninsular state alone is enough: COVERED.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>Fixed customer texts (copied from apps/prompts/khind_prompts.py)</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="9" t="n"/>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>Location question</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>Boleh kongsikan Poskod &amp; Kawasan pemasangan untuk saya semak liputan penghantaran percuma? 😊</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="27" customHeight="1">
+    <row r="53">
       <c r="A53" s="9" t="n"/>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Covered line + kerja question</t>
+          <t>Location question</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Baik, kawasan [Kawasan/Poskod] ada dalam liputan penghantaran &amp; pemasangan kami! 🚚✨ Boleh saya tahu cik/tuan bekerja sekarang?</t>
+          <t>Boleh kongsikan Poskod &amp; Kawasan pemasangan untuk saya semak liputan penghantaran percuma? 😊</t>
         </is>
       </c>
     </row>
@@ -4213,38 +4213,38 @@
       <c r="A54" s="9" t="n"/>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Not-covered handoff line</t>
+          <t>Covered line + kerja question</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Maaf sangat cik/tuan, kawasan [Kawasan] belum ada liputan KHIND buat masa ini. 🙏 Pegawai kami akan hubungi cik/tuan nanti ya.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
+          <t>Baik, kawasan [Kawasan/Poskod] ada dalam liputan penghantaran &amp; pemasangan kami! 🚚✨ Boleh saya tahu cik/tuan bekerja sekarang?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="27" customHeight="1">
       <c r="A55" s="9" t="n"/>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>RM1 line (working)</t>
+          <t>Not-covered handoff line</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Terbaik! 👍 *Pendaftaran hanya RM1*, tiada bayaran lain sekarang. Jom semak kelayakan dulu?</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="27" customHeight="1">
+          <t>Maaf sangat cik/tuan, kawasan [Kawasan] belum ada liputan KHIND buat masa ini. 🙏 Pegawai kami akan hubungi cik/tuan nanti ya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
       <c r="A56" s="9" t="n"/>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Not-working handoff line</t>
+          <t>RM1 line (working)</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Faham, cik/tuan. Skim ini memerlukan pemohon yang bekerja. Saya sambungkan cik/tuan kepada pegawai kami untuk bantuan lanjut ya 🙏</t>
+          <t>Terbaik! 👍 *Pendaftaran hanya RM1*, tiada bayaran lain sekarang. Jom semak kelayakan dulu?</t>
         </is>
       </c>
     </row>
@@ -4252,12 +4252,12 @@
       <c r="A57" s="9" t="n"/>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Missing-fact line (not a handoff)</t>
+          <t>Not-working handoff line</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Maaf, maklumat [topik] belum ada dalam sistem saya. Pegawai kami akan sahkan dengan cik/tuan nanti ya 🙏   ([topik] is filled in; the pending question follows)</t>
+          <t>Faham, cik/tuan. Skim ini memerlukan pemohon yang bekerja. Saya sambungkan cik/tuan kepada pegawai kami untuk bantuan lanjut ya 🙏</t>
         </is>
       </c>
     </row>
@@ -4265,25 +4265,25 @@
       <c r="A58" s="9" t="n"/>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Form-complete line</t>
+          <t>Missing-fact line (not a handoff)</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Terima kasih, butiran permohonan cik/tuan sudah lengkap! 👍 Boleh hantar *gambar IC depan &amp; belakang* sekarang? 📸</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
+          <t>Maaf, maklumat [topik] belum ada dalam sistem saya. Pegawai kami akan sahkan dengan cik/tuan nanti ya 🙏   ([topik] is filled in; the pending question follows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="27" customHeight="1">
       <c r="A59" s="9" t="n"/>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Town question (need_town)</t>
+          <t>Form-complete line</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Boleh kongsikan nama bandar atau kawasan pemasangan cik/tuan di Sabah/Sarawak? 😊</t>
+          <t>Terima kasih, butiran permohonan cik/tuan sudah lengkap! 👍 Boleh hantar *gambar IC depan &amp; belakang* sekarang? 📸</t>
         </is>
       </c>
     </row>
@@ -4291,12 +4291,12 @@
       <c r="A60" s="9" t="n"/>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Postcode question (need_state)</t>
+          <t>Town question (need_town)</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Boleh kongsikan poskod kawasan pemasangan cik/tuan? 😊</t>
+          <t>Boleh kongsikan nama bandar atau kawasan pemasangan cik/tuan di Sabah/Sarawak? 😊</t>
         </is>
       </c>
     </row>
@@ -4304,12 +4304,12 @@
       <c r="A61" s="9" t="n"/>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Kerja question (alone)</t>
+          <t>Postcode question (need_state)</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Boleh saya tahu cik/tuan bekerja sekarang? 😊</t>
+          <t>Boleh kongsikan poskod kawasan pemasangan cik/tuan? 😊</t>
         </is>
       </c>
     </row>
@@ -4317,23 +4317,36 @@
       <c r="A62" s="9" t="n"/>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>IC-photo question (after the form)</t>
+          <t>Kerja question (alone)</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Boleh hantar *gambar IC depan &amp; belakang* sekarang? 📸</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="216" customHeight="1">
+          <t>Boleh saya tahu cik/tuan bekerja sekarang? 😊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
       <c r="A63" s="9" t="n"/>
       <c r="B63" s="9" t="inlineStr">
         <is>
+          <t>IC-photo question (after the form)</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Boleh hantar *gambar IC depan &amp; belakang* sekarang? 📸</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="216" customHeight="1">
+      <c r="A64" s="9" t="n"/>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
           <t>Product list (copy exactly)</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>❄️ *Peti Sejuk*
 1️⃣ ChillMaster 592L (Side-by-Side)
@@ -4349,64 +4362,64 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="27" customHeight="1">
-      <c r="A64" s="9" t="n"/>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>Fallback line: coverage-unsupported-alternative</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t>Maaf sangat cik/tuan, kawasan cik/tuan belum ada liputan KHIND buat masa ini. 🙏 Pegawai kami akan hubungi cik/tuan nanti ya.   (sent by code only when the model writes nothing)</t>
-        </is>
-      </c>
-    </row>
     <row r="65" ht="27" customHeight="1">
       <c r="A65" s="9" t="n"/>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Fallback line: not-working</t>
+          <t>Fallback line: coverage-unsupported-alternative</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Faham, cik/tuan. Skim ini memerlukan pemohon yang bekerja. Saya sambungkan cik/tuan kepada pegawai kami untuk bantuan lanjut ya 🙏   (sent by code only when the model writes nothing)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
+          <t>Maaf sangat cik/tuan, kawasan cik/tuan belum ada liputan KHIND buat masa ini. 🙏 Pegawai kami akan hubungi cik/tuan nanti ya.   (sent by code only when the model writes nothing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="27" customHeight="1">
       <c r="A66" s="9" t="n"/>
       <c r="B66" s="9" t="inlineStr">
         <is>
+          <t>Fallback line: not-working</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Faham, cik/tuan. Skim ini memerlukan pemohon yang bekerja. Saya sambungkan cik/tuan kepada pegawai kami untuk bantuan lanjut ya 🙏   (sent by code only when the model writes nothing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="n"/>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
           <t>Fallback line: other labels</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>Baik, saya sambungkan cik/tuan kepada pegawai kami ya. 🙏</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t>Fixed USP blocks - must appear word for word, once, on a first pick</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="108" customHeight="1">
-      <c r="A68" s="9" t="inlineStr">
+    <row r="69" ht="108" customHeight="1">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>chillmaster_592l  (4 ✅ lines)</t>
         </is>
       </c>
-      <c r="C68" s="9" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
         <is>
           <t>*KHIND ChillMaster 592L* ✨
 ✅ Kapasiti besar 592L dengan susunan rak boleh laras, sesuai untuk keluarga besar.
@@ -4416,18 +4429,18 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="94.5" customHeight="1">
-      <c r="A69" s="9" t="inlineStr">
+    <row r="70" ht="94.5" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B69" s="9" t="inlineStr">
+      <c r="B70" s="9" t="inlineStr">
         <is>
           <t>chillmaster_lite_480l  (4 ✅ lines)</t>
         </is>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C70" s="9" t="inlineStr">
         <is>
           <t>*KHIND ChillMaster Lite 480L* ✨
 ✅ Kapasiti besar 480L - ruang simpanan luas untuk seisi keluarga.
@@ -4437,18 +4450,18 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="121.5" customHeight="1">
-      <c r="A70" s="9" t="inlineStr">
+    <row r="71" ht="121.5" customHeight="1">
+      <c r="A71" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr">
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>chillmaster_x_466l  (5 ✅ lines)</t>
         </is>
       </c>
-      <c r="C70" s="9" t="inlineStr">
+      <c r="C71" s="9" t="inlineStr">
         <is>
           <t>*KHIND ChillMaster X 466L* ✨
 ✅ Kapasiti besar 466L dengan rekaan moden Multi-Door 4 pintu.
@@ -4459,18 +4472,18 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="148.5" customHeight="1">
-      <c r="A71" s="9" t="inlineStr">
+    <row r="72" ht="148.5" customHeight="1">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B71" s="9" t="inlineStr">
+      <c r="B72" s="9" t="inlineStr">
         <is>
           <t>washer_dryer_11_7  (7 ✅ lines)</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C72" s="9" t="inlineStr">
         <is>
           <t>*2-in-1 Washer Dryer KHIND 11KG/7KG* ✨
 ✅ Kapasiti besar - 11KG basuh &amp; 7KG kering
@@ -4483,18 +4496,18 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="148.5" customHeight="1">
-      <c r="A72" s="9" t="inlineStr">
+    <row r="73" ht="148.5" customHeight="1">
+      <c r="A73" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B72" s="9" t="inlineStr">
+      <c r="B73" s="9" t="inlineStr">
         <is>
           <t>front_load_9kg  (6 ✅ lines)</t>
         </is>
       </c>
-      <c r="C72" s="9" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
         <is>
           <t>*KHIND Front Load Washer 9KG* ✨
 ✅ Kapasiti basuhan 9KG
@@ -4507,18 +4520,18 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="135" customHeight="1">
-      <c r="A73" s="9" t="inlineStr">
+    <row r="74" ht="135" customHeight="1">
+      <c r="A74" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B73" s="9" t="inlineStr">
+      <c r="B74" s="9" t="inlineStr">
         <is>
           <t>ecowash_top_15kg  (5 ✅ lines)</t>
         </is>
       </c>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="C74" s="9" t="inlineStr">
         <is>
           <t>*KHIND EcoWash Top Load 15KG* ✨
 ✅ Kapasiti besar 15KG - boleh basuh banyak pakaian sekali gus
@@ -4530,18 +4543,18 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="148.5" customHeight="1">
-      <c r="A74" s="9" t="inlineStr">
+    <row r="75" ht="148.5" customHeight="1">
+      <c r="A75" s="9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B74" s="9" t="inlineStr">
+      <c r="B75" s="9" t="inlineStr">
         <is>
           <t>drymaster_9kg  (6 ✅ lines)</t>
         </is>
       </c>
-      <c r="C74" s="9" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>*KHIND DryMaster 9KG (Heat Pump Dryer)* ✨
 ✅ Kapasiti pengeringan 9KG
@@ -4554,18 +4567,18 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="108" customHeight="1">
-      <c r="A75" s="9" t="inlineStr">
+    <row r="76" ht="108" customHeight="1">
+      <c r="A76" s="9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
+      <c r="B76" s="9" t="inlineStr">
         <is>
           <t>aircond_kool_series  (4 ✅ lines)</t>
         </is>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C76" s="9" t="inlineStr">
         <is>
           <t>*KHIND KOOL Series Air Conditioner* ✨
 ✅ Inverter + 5 Bintang Tenaga - sejuk konsisten, kurang bunyi dan lebih jimat elektrik.
@@ -4575,21 +4588,21 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="8" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>BORANG template - must appear exactly (only the Produk value changes)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="378" customHeight="1">
-      <c r="A77" s="9" t="n"/>
-      <c r="B77" s="9" t="inlineStr">
+    <row r="78" ht="378" customHeight="1">
+      <c r="A78" s="9" t="n"/>
+      <c r="B78" s="9" t="inlineStr">
         <is>
           <t>BORANG PERMOHONAN KHIND</t>
         </is>
       </c>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="C78" s="9" t="inlineStr">
         <is>
           <t>BORANG PERMOHONAN KHIND
 =========================
@@ -4615,36 +4628,23 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="8" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>Known open issues to watch (2026-09-24, after rerun 2)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="40.5" customHeight="1">
-      <c r="A79" s="9" t="n"/>
-      <c r="B79" s="9" t="inlineStr">
-        <is>
-          <t>Coverage handoff (B2, B5-B7, B12)</t>
-        </is>
-      </c>
-      <c r="C79" s="9" t="inlineStr">
-        <is>
-          <t>Changed after rerun 2: advance_purchase_stage hands over itself. Rerun 2 had B12 with no handoff and a USP on top, and B6 with the model's English reasoning as the reply. Check the Function Response and State, and that the reply is only the not-covered line.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
+    <row r="80" ht="40.5" customHeight="1">
       <c r="A80" s="9" t="n"/>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Out-of-range items (D6)</t>
+          <t>Coverage handoff (B2, B5-B7, B12)</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Rerun 2 said "8 produk dalam senarai kami" without the list.</t>
+          <t>Changed after rerun 2: advance_purchase_stage hands over itself. Rerun 2 had B12 with no handoff and a USP on top, and B6 with the model's English reasoning as the reply. Check the Function Response and State, and that the reply is only the not-covered line.</t>
         </is>
       </c>
     </row>
@@ -4652,38 +4652,38 @@
       <c r="A81" s="9" t="n"/>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Style (E4)</t>
+          <t>Out-of-range items (D6)</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Rerun 2: no bold in A4, no emoji in A11 and F6. Now every reply needs an emoji; bold is only for key terms.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="40.5" customHeight="1">
+          <t>Rerun 2 said "8 produk dalam senarai kami" without the list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
       <c r="A82" s="9" t="n"/>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Cross-product figures (A3, G6)</t>
+          <t>Style (E4)</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Failed on the first 2026-09-24 run: whole-corpus search returned the ChillMaster Lite 480L document. Searches are now limited to the product's own document (Function Response: scope 'product'). Quoting RM75/RM95 or 80kg/87kg for the 592L is still a Critical Fail.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="27" customHeight="1">
+          <t>Rerun 2: no bold in A4, no emoji in A11 and F6. Now every reply needs an emoji; bold is only for key terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="40.5" customHeight="1">
       <c r="A83" s="9" t="n"/>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>DryMaster prices (D2, C8)</t>
+          <t>Cross-product figures (A3, G6)</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>The DryMaster document holds two conflicting price tables (RM85/month x 48, or RM105 x 48 and RM135 x 36). Either traces to the DryMaster document: not a Fail, but note it.</t>
+          <t>Failed on the first 2026-09-24 run: whole-corpus search returned the ChillMaster Lite 480L document. Searches are now limited to the product's own document (Function Response: scope 'product'). Quoting RM75/RM95 or 80kg/87kg for the 592L is still a Critical Fail.</t>
         </is>
       </c>
     </row>
@@ -4691,25 +4691,25 @@
       <c r="A84" s="9" t="n"/>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>PDPA name echo (A8)</t>
+          <t>DryMaster prices (D2, C8)</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>The model thanked customers by name on 2026-09-20 and 2026-09-24, and in scripted form-step runs after rerun 2. Read the reply word by word.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
+          <t>The DryMaster document holds two conflicting price tables (RM85/month x 48, or RM105 x 48 and RM135 x 36). Either traces to the DryMaster document: not a Fail, but note it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="27" customHeight="1">
       <c r="A85" s="9" t="n"/>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Duplicate blank form (A11)</t>
+          <t>PDPA name echo (A8)</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>The full blank form was resent after completion on 2026-09-20.</t>
+          <t>The model thanked customers by name on 2026-09-20 and 2026-09-24, and in scripted form-step runs after rerun 2. Code now removes the customer's personal values from every reply. Still read the reply word by word.</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       <c r="A86" s="9" t="n"/>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Duplicate USP on a switch (G5, G7)</t>
+          <t>Duplicate blank form (A11)</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>The model sometimes writes its own product description; code strips it. Count the ✅ lines against this sheet.</t>
+          <t>The full blank form was resent after completion on 2026-09-20.</t>
         </is>
       </c>
     </row>
@@ -4730,10 +4730,23 @@
       <c r="A87" s="9" t="n"/>
       <c r="B87" s="9" t="inlineStr">
         <is>
+          <t>Duplicate USP on a switch (G5, G7)</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>The model sometimes writes its own product description; code strips it. Count the ✅ lines against this sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="n"/>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
           <t>Employment rules (F9, F10)</t>
         </is>
       </c>
-      <c r="C87" s="9" t="inlineStr">
+      <c r="C88" s="9" t="inlineStr">
         <is>
           <t>Confirmed 2026-09-24: pensioner = not working, self-employed = working.</t>
         </is>
@@ -4741,17 +4754,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A79:C79"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A77:C77"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A52:C52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
